--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run6/epoch_40/per_file_predictions_epoch_40.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run6/epoch_40/per_file_predictions_epoch_40.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="522">
   <si>
     <t>Filename</t>
   </si>
@@ -808,769 +808,778 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.8694,0.0552,0.0136,0.0287</t>
-  </si>
-  <si>
-    <t>0.0235,0.0019,0.0026,0.9888</t>
-  </si>
-  <si>
-    <t>0.6811,0.0058,0.0011,0.4329</t>
-  </si>
-  <si>
-    <t>0.0626,0.0011,0.0018,0.9770</t>
-  </si>
-  <si>
-    <t>0.9971,0.0009,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.9931,0.0033,0.0002,0.0009</t>
-  </si>
-  <si>
-    <t>0.9920,0.0040,0.0004,0.0010</t>
-  </si>
-  <si>
-    <t>0.9974,0.0010,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9914,0.0040,0.0002,0.0013</t>
-  </si>
-  <si>
-    <t>0.9937,0.0030,0.0006,0.0007</t>
-  </si>
-  <si>
-    <t>0.9874,0.0095,0.0016,0.0010</t>
-  </si>
-  <si>
-    <t>0.9949,0.0017,0.0002,0.0008</t>
-  </si>
-  <si>
-    <t>0.5113,0.0798,0.5311,0.0121</t>
-  </si>
-  <si>
-    <t>0.2672,0.0679,0.7159,0.0116</t>
-  </si>
-  <si>
-    <t>0.3440,0.0334,0.7555,0.0015</t>
-  </si>
-  <si>
-    <t>0.3225,0.0585,0.6299,0.0048</t>
-  </si>
-  <si>
-    <t>0.7148,0.0905,0.2262,0.0086</t>
-  </si>
-  <si>
-    <t>0.0131,0.9799,0.0080,0.0003</t>
-  </si>
-  <si>
-    <t>0.0250,0.9664,0.0192,0.0009</t>
-  </si>
-  <si>
-    <t>0.3040,0.7397,0.0428,0.0033</t>
-  </si>
-  <si>
-    <t>0.0876,0.9132,0.0220,0.0016</t>
-  </si>
-  <si>
-    <t>0.0077,0.9814,0.0202,0.0002</t>
-  </si>
-  <si>
-    <t>0.6830,0.0147,0.2175,0.0565</t>
-  </si>
-  <si>
-    <t>0.4661,0.0597,0.4898,0.0442</t>
-  </si>
-  <si>
-    <t>0.0757,0.0158,0.9273,0.0033</t>
-  </si>
-  <si>
-    <t>0.2079,0.0198,0.8638,0.0018</t>
-  </si>
-  <si>
-    <t>0.1408,0.0074,0.8824,0.0063</t>
-  </si>
-  <si>
-    <t>0.1078,0.0046,0.8594,0.0316</t>
-  </si>
-  <si>
-    <t>0.0104,0.0035,0.9800,0.0107</t>
-  </si>
-  <si>
-    <t>0.4303,0.6030,0.0336,0.0036</t>
-  </si>
-  <si>
-    <t>0.7075,0.1082,0.2125,0.0025</t>
-  </si>
-  <si>
-    <t>0.0115,0.0267,0.9839,0.0011</t>
-  </si>
-  <si>
-    <t>0.0021,0.9868,0.0296,0.0001</t>
-  </si>
-  <si>
-    <t>0.8209,0.1112,0.0741,0.0102</t>
-  </si>
-  <si>
-    <t>0.7247,0.1354,0.1446,0.0183</t>
-  </si>
-  <si>
-    <t>0.5946,0.3163,0.1115,0.0033</t>
-  </si>
-  <si>
-    <t>0.1245,0.8118,0.2531,0.0048</t>
-  </si>
-  <si>
-    <t>0.0069,0.7433,0.7700,0.0052</t>
-  </si>
-  <si>
-    <t>0.0088,0.0335,0.9193,0.1120</t>
-  </si>
-  <si>
-    <t>0.0846,0.0482,0.7501,0.2063</t>
-  </si>
-  <si>
-    <t>0.0249,0.0064,0.9232,0.0923</t>
-  </si>
-  <si>
-    <t>0.0193,0.1521,0.9541,0.0011</t>
-  </si>
-  <si>
-    <t>0.0049,0.9586,0.0453,0.0017</t>
-  </si>
-  <si>
-    <t>0.0105,0.0329,0.9712,0.0044</t>
-  </si>
-  <si>
-    <t>0.1994,0.6716,0.0323,0.2009</t>
-  </si>
-  <si>
-    <t>0.0075,0.9675,0.0087,0.0168</t>
-  </si>
-  <si>
-    <t>0.0102,0.9205,0.3044,0.0054</t>
-  </si>
-  <si>
-    <t>0.0106,0.9596,0.1455,0.0057</t>
-  </si>
-  <si>
-    <t>0.0052,0.4004,0.7902,0.0547</t>
-  </si>
-  <si>
-    <t>0.0067,0.2571,0.9678,0.0014</t>
-  </si>
-  <si>
-    <t>0.0944,0.0046,0.8916,0.0287</t>
-  </si>
-  <si>
-    <t>0.0592,0.0007,0.8476,0.0702</t>
-  </si>
-  <si>
-    <t>0.0103,0.0131,0.9700,0.0104</t>
-  </si>
-  <si>
-    <t>0.0606,0.0721,0.9334,0.0027</t>
-  </si>
-  <si>
-    <t>0.8764,0.1344,0.0233,0.0038</t>
-  </si>
-  <si>
-    <t>0.9550,0.0215,0.0135,0.0053</t>
-  </si>
-  <si>
-    <t>0.9912,0.0040,0.0008,0.0010</t>
-  </si>
-  <si>
-    <t>0.0135,0.0246,0.9790,0.0050</t>
-  </si>
-  <si>
-    <t>0.9717,0.0146,0.0055,0.0029</t>
-  </si>
-  <si>
-    <t>0.9789,0.0185,0.0016,0.0018</t>
-  </si>
-  <si>
-    <t>0.9456,0.0744,0.0042,0.0013</t>
-  </si>
-  <si>
-    <t>0.0008,0.9265,0.9157,0.0002</t>
-  </si>
-  <si>
-    <t>0.0023,0.0102,0.9694,0.0599</t>
-  </si>
-  <si>
-    <t>0.0041,0.0309,0.9791,0.0082</t>
-  </si>
-  <si>
-    <t>0.0003,0.9402,0.9744,0.0001</t>
-  </si>
-  <si>
-    <t>0.0008,0.0027,0.9917,0.0096</t>
-  </si>
-  <si>
-    <t>0.0176,0.7709,0.6495,0.0014</t>
-  </si>
-  <si>
-    <t>0.0070,0.9799,0.0158,0.0001</t>
-  </si>
-  <si>
-    <t>0.9106,0.0147,0.0545,0.0060</t>
-  </si>
-  <si>
-    <t>0.5693,0.4463,0.0563,0.0314</t>
-  </si>
-  <si>
-    <t>0.0025,0.0151,0.9933,0.0005</t>
-  </si>
-  <si>
-    <t>0.0009,0.9181,0.9190,0.0004</t>
-  </si>
-  <si>
-    <t>0.0010,0.9049,0.9343,0.0001</t>
-  </si>
-  <si>
-    <t>0.0005,0.9803,0.5604,0.0003</t>
-  </si>
-  <si>
-    <t>0.0002,0.9788,0.8335,0.0001</t>
-  </si>
-  <si>
-    <t>0.0065,0.0031,0.0297,0.9867</t>
-  </si>
-  <si>
-    <t>0.0017,0.0036,0.0021,0.9977</t>
-  </si>
-  <si>
-    <t>0.0016,0.0012,0.0005,0.9989</t>
-  </si>
-  <si>
-    <t>0.0063,0.0036,0.0038,0.9945</t>
-  </si>
-  <si>
-    <t>0.0210,0.0149,0.0035,0.9869</t>
-  </si>
-  <si>
-    <t>0.0035,0.0017,0.0007,0.9979</t>
-  </si>
-  <si>
-    <t>0.0007,0.9776,0.7061,0.0004</t>
-  </si>
-  <si>
-    <t>0.0011,0.7873,0.9750,0.0001</t>
-  </si>
-  <si>
-    <t>0.0179,0.4678,0.8324,0.0039</t>
-  </si>
-  <si>
-    <t>0.0055,0.7158,0.9155,0.0016</t>
-  </si>
-  <si>
-    <t>0.0004,0.9636,0.9119,0.0001</t>
-  </si>
-  <si>
-    <t>0.0066,0.8966,0.7823,0.0031</t>
-  </si>
-  <si>
-    <t>0.9786,0.0133,0.0044,0.0028</t>
-  </si>
-  <si>
-    <t>0.9830,0.0262,0.0007,0.0004</t>
-  </si>
-  <si>
-    <t>0.9878,0.0085,0.0008,0.0011</t>
-  </si>
-  <si>
-    <t>0.9585,0.0353,0.0093,0.0028</t>
-  </si>
-  <si>
-    <t>0.9773,0.0279,0.0015,0.0010</t>
-  </si>
-  <si>
-    <t>0.9833,0.0075,0.0048,0.0014</t>
-  </si>
-  <si>
-    <t>0.9730,0.0345,0.0018,0.0012</t>
-  </si>
-  <si>
-    <t>0.9475,0.0973,0.0041,0.0004</t>
-  </si>
-  <si>
-    <t>0.9904,0.0009,0.0001,0.0055</t>
-  </si>
-  <si>
-    <t>0.9877,0.0074,0.0016,0.0009</t>
-  </si>
-  <si>
-    <t>0.9871,0.0027,0.0005,0.0041</t>
-  </si>
-  <si>
-    <t>0.9933,0.0005,0.0002,0.0027</t>
-  </si>
-  <si>
-    <t>0.9945,0.0040,0.0002,0.0004</t>
-  </si>
-  <si>
-    <t>0.9859,0.0119,0.0020,0.0007</t>
-  </si>
-  <si>
-    <t>0.9949,0.0017,0.0002,0.0009</t>
-  </si>
-  <si>
-    <t>0.9952,0.0006,0.0001,0.0017</t>
-  </si>
-  <si>
-    <t>0.0268,0.0037,0.9758,0.0038</t>
-  </si>
-  <si>
-    <t>0.1260,0.0265,0.8965,0.0012</t>
-  </si>
-  <si>
-    <t>0.8331,0.0058,0.1694,0.0099</t>
-  </si>
-  <si>
-    <t>0.0922,0.0077,0.9079,0.0098</t>
-  </si>
-  <si>
-    <t>0.0300,0.9605,0.0071,0.0009</t>
-  </si>
-  <si>
-    <t>0.0137,0.9714,0.0539,0.0003</t>
-  </si>
-  <si>
-    <t>0.0381,0.9610,0.0039,0.0007</t>
-  </si>
-  <si>
-    <t>0.4334,0.6347,0.0210,0.0022</t>
-  </si>
-  <si>
-    <t>0.1789,0.8667,0.0184,0.0019</t>
-  </si>
-  <si>
-    <t>0.0036,0.9912,0.0034,0.0002</t>
-  </si>
-  <si>
-    <t>0.4941,0.6228,0.0133,0.0008</t>
-  </si>
-  <si>
-    <t>0.7709,0.0862,0.1179,0.0143</t>
-  </si>
-  <si>
-    <t>0.4035,0.0266,0.6917,0.0070</t>
-  </si>
-  <si>
-    <t>0.5947,0.1955,0.1471,0.0075</t>
-  </si>
-  <si>
-    <t>0.6550,0.0392,0.3637,0.0173</t>
-  </si>
-  <si>
-    <t>0.0720,0.0368,0.1189,0.8979</t>
-  </si>
-  <si>
-    <t>0.0084,0.9816,0.0303,0.0008</t>
-  </si>
-  <si>
-    <t>0.0133,0.9629,0.0134,0.0090</t>
-  </si>
-  <si>
-    <t>0.1912,0.6042,0.0229,0.2850</t>
-  </si>
-  <si>
-    <t>0.0011,0.9071,0.9447,0.0004</t>
-  </si>
-  <si>
-    <t>0.0174,0.9643,0.0995,0.0005</t>
-  </si>
-  <si>
-    <t>0.2620,0.4824,0.2620,0.0010</t>
-  </si>
-  <si>
-    <t>0.0908,0.9199,0.0179,0.0005</t>
-  </si>
-  <si>
-    <t>0.9598,0.0193,0.0115,0.0041</t>
-  </si>
-  <si>
-    <t>0.9823,0.0039,0.0012,0.0051</t>
-  </si>
-  <si>
-    <t>0.9538,0.0137,0.0156,0.0102</t>
-  </si>
-  <si>
-    <t>0.9696,0.0186,0.0045,0.0051</t>
-  </si>
-  <si>
-    <t>0.9839,0.0034,0.0024,0.0033</t>
-  </si>
-  <si>
-    <t>0.9766,0.0089,0.0064,0.0019</t>
-  </si>
-  <si>
-    <t>0.9769,0.0072,0.0061,0.0033</t>
-  </si>
-  <si>
-    <t>0.9880,0.0033,0.0022,0.0015</t>
-  </si>
-  <si>
-    <t>0.0027,0.7308,0.9108,0.0012</t>
-  </si>
-  <si>
-    <t>0.0047,0.6949,0.9492,0.0010</t>
-  </si>
-  <si>
-    <t>0.0112,0.1709,0.9517,0.0010</t>
-  </si>
-  <si>
-    <t>0.0206,0.1698,0.9440,0.0008</t>
-  </si>
-  <si>
-    <t>0.3563,0.0493,0.5071,0.1660</t>
-  </si>
-  <si>
-    <t>0.8257,0.0101,0.0910,0.0379</t>
-  </si>
-  <si>
-    <t>0.3378,0.0081,0.7976,0.0042</t>
-  </si>
-  <si>
-    <t>0.6513,0.0923,0.2542,0.0176</t>
-  </si>
-  <si>
-    <t>0.0193,0.0010,0.0004,0.9928</t>
-  </si>
-  <si>
-    <t>0.0002,0.0007,0.0002,0.9997</t>
-  </si>
-  <si>
-    <t>0.0035,0.0024,0.0007,0.9980</t>
-  </si>
-  <si>
-    <t>0.0096,0.0016,0.0016,0.9949</t>
-  </si>
-  <si>
-    <t>0.0030,0.9338,0.2605,0.0037</t>
-  </si>
-  <si>
-    <t>0.9816,0.0068,0.0024,0.0035</t>
-  </si>
-  <si>
-    <t>0.6487,0.3881,0.0060,0.0136</t>
-  </si>
-  <si>
-    <t>0.9666,0.0227,0.0020,0.0036</t>
-  </si>
-  <si>
-    <t>0.7785,0.2726,0.0212,0.0008</t>
-  </si>
-  <si>
-    <t>0.9548,0.0121,0.0042,0.0124</t>
-  </si>
-  <si>
-    <t>0.6308,0.0468,0.0152,0.2795</t>
-  </si>
-  <si>
-    <t>0.9496,0.0284,0.0195,0.0015</t>
-  </si>
-  <si>
-    <t>0.0143,0.0486,0.9345,0.0676</t>
-  </si>
-  <si>
-    <t>0.9001,0.0002,0.0025,0.0976</t>
-  </si>
-  <si>
-    <t>0.9481,0.0004,0.0022,0.0336</t>
-  </si>
-  <si>
-    <t>0.2560,0.7323,0.0328,0.0122</t>
-  </si>
-  <si>
-    <t>0.8424,0.1371,0.0128,0.0067</t>
-  </si>
-  <si>
-    <t>0.9168,0.0455,0.0334,0.0011</t>
-  </si>
-  <si>
-    <t>0.4955,0.3979,0.0382,0.0736</t>
-  </si>
-  <si>
-    <t>0.8527,0.0810,0.0756,0.0048</t>
-  </si>
-  <si>
-    <t>0.8458,0.0755,0.0510,0.0087</t>
-  </si>
-  <si>
-    <t>0.9857,0.0023,0.0015,0.0038</t>
-  </si>
-  <si>
-    <t>0.9816,0.0140,0.0024,0.0015</t>
-  </si>
-  <si>
-    <t>0.9881,0.0022,0.0016,0.0025</t>
-  </si>
-  <si>
-    <t>0.9702,0.0115,0.0029,0.0064</t>
-  </si>
-  <si>
-    <t>0.9655,0.0030,0.0037,0.0154</t>
-  </si>
-  <si>
-    <t>0.9744,0.0132,0.0035,0.0031</t>
-  </si>
-  <si>
-    <t>0.9751,0.0063,0.0080,0.0029</t>
-  </si>
-  <si>
-    <t>0.9906,0.0020,0.0010,0.0018</t>
-  </si>
-  <si>
-    <t>0.5667,0.5413,0.0173,0.0101</t>
-  </si>
-  <si>
-    <t>0.5201,0.5752,0.0211,0.0012</t>
-  </si>
-  <si>
-    <t>0.2217,0.8479,0.0062,0.0012</t>
-  </si>
-  <si>
-    <t>0.7938,0.1522,0.0997,0.0152</t>
-  </si>
-  <si>
-    <t>0.9231,0.1173,0.0106,0.0012</t>
-  </si>
-  <si>
-    <t>0.9155,0.0526,0.0214,0.0097</t>
-  </si>
-  <si>
-    <t>0.9830,0.0104,0.0012,0.0017</t>
-  </si>
-  <si>
-    <t>0.8192,0.1761,0.0354,0.0112</t>
-  </si>
-  <si>
-    <t>0.0010,0.0180,0.9962,0.0010</t>
-  </si>
-  <si>
-    <t>0.8057,0.1863,0.0446,0.0036</t>
-  </si>
-  <si>
-    <t>0.0138,0.1888,0.9212,0.0010</t>
-  </si>
-  <si>
-    <t>0.0091,0.2319,0.9557,0.0012</t>
-  </si>
-  <si>
-    <t>0.1275,0.0145,0.9032,0.0044</t>
-  </si>
-  <si>
-    <t>0.0188,0.1385,0.9282,0.0139</t>
-  </si>
-  <si>
-    <t>0.0058,0.0173,0.9826,0.0037</t>
-  </si>
-  <si>
-    <t>0.0089,0.0024,0.9833,0.0129</t>
-  </si>
-  <si>
-    <t>0.0191,0.0343,0.9750,0.0006</t>
-  </si>
-  <si>
-    <t>0.1570,0.1451,0.7611,0.0263</t>
-  </si>
-  <si>
-    <t>0.2875,0.0156,0.7958,0.0035</t>
-  </si>
-  <si>
-    <t>0.8205,0.0348,0.1076,0.0118</t>
-  </si>
-  <si>
-    <t>0.1632,0.0548,0.8450,0.0022</t>
-  </si>
-  <si>
-    <t>0.0993,0.3761,0.5344,0.0011</t>
-  </si>
-  <si>
-    <t>0.7651,0.0875,0.0959,0.0078</t>
-  </si>
-  <si>
-    <t>0.4410,0.3662,0.3201,0.0747</t>
-  </si>
-  <si>
-    <t>0.6252,0.0491,0.3973,0.0073</t>
-  </si>
-  <si>
-    <t>0.9533,0.0610,0.0061,0.0007</t>
-  </si>
-  <si>
-    <t>0.4062,0.7100,0.0068,0.0006</t>
-  </si>
-  <si>
-    <t>0.6711,0.4128,0.0013,0.0034</t>
-  </si>
-  <si>
-    <t>0.8934,0.2196,0.0026,0.0008</t>
-  </si>
-  <si>
-    <t>0.3297,0.6931,0.0286,0.0016</t>
-  </si>
-  <si>
-    <t>0.4145,0.1457,0.5270,0.0304</t>
-  </si>
-  <si>
-    <t>0.8459,0.0029,0.1972,0.0037</t>
-  </si>
-  <si>
-    <t>0.7503,0.0212,0.0806,0.0863</t>
-  </si>
-  <si>
-    <t>0.6361,0.0221,0.2234,0.0882</t>
-  </si>
-  <si>
-    <t>0.7230,0.0086,0.3121,0.0171</t>
-  </si>
-  <si>
-    <t>0.0042,0.0048,0.9820,0.0232</t>
-  </si>
-  <si>
-    <t>0.0273,0.1747,0.6752,0.2070</t>
-  </si>
-  <si>
-    <t>0.0345,0.2178,0.8933,0.0090</t>
-  </si>
-  <si>
-    <t>0.0876,0.1986,0.8220,0.0442</t>
-  </si>
-  <si>
-    <t>0.0207,0.8113,0.3694,0.0036</t>
-  </si>
-  <si>
-    <t>0.9896,0.0078,0.0005,0.0008</t>
-  </si>
-  <si>
-    <t>0.9842,0.0066,0.0047,0.0011</t>
-  </si>
-  <si>
-    <t>0.9912,0.0028,0.0002,0.0020</t>
-  </si>
-  <si>
-    <t>0.9767,0.0209,0.0021,0.0015</t>
-  </si>
-  <si>
-    <t>0.9416,0.0470,0.0205,0.0044</t>
-  </si>
-  <si>
-    <t>0.9945,0.0021,0.0003,0.0008</t>
-  </si>
-  <si>
-    <t>0.9890,0.0025,0.0004,0.0026</t>
-  </si>
-  <si>
-    <t>0.9926,0.0013,0.0007,0.0016</t>
-  </si>
-  <si>
-    <t>0.2181,0.0759,0.7781,0.0065</t>
-  </si>
-  <si>
-    <t>0.2341,0.4763,0.3844,0.0147</t>
-  </si>
-  <si>
-    <t>0.6314,0.0195,0.3206,0.0394</t>
-  </si>
-  <si>
-    <t>0.0049,0.0464,0.9828,0.0019</t>
-  </si>
-  <si>
-    <t>0.0119,0.0281,0.9806,0.0007</t>
-  </si>
-  <si>
-    <t>0.1967,0.4144,0.2726,0.0064</t>
-  </si>
-  <si>
-    <t>0.0006,0.0058,0.9970,0.0008</t>
-  </si>
-  <si>
-    <t>0.0405,0.0278,0.9286,0.0072</t>
-  </si>
-  <si>
-    <t>0.0305,0.0187,0.9631,0.0031</t>
-  </si>
-  <si>
-    <t>0.0128,0.0266,0.9546,0.0169</t>
-  </si>
-  <si>
-    <t>0.0929,0.2649,0.7511,0.0120</t>
-  </si>
-  <si>
-    <t>0.6416,0.0103,0.2249,0.0650</t>
-  </si>
-  <si>
-    <t>0.6174,0.0074,0.4812,0.0058</t>
-  </si>
-  <si>
-    <t>0.8372,0.0111,0.1249,0.0107</t>
-  </si>
-  <si>
-    <t>0.9742,0.0097,0.0013,0.0057</t>
-  </si>
-  <si>
-    <t>0.9893,0.0072,0.0011,0.0007</t>
-  </si>
-  <si>
-    <t>0.9894,0.0082,0.0016,0.0006</t>
-  </si>
-  <si>
-    <t>0.9792,0.0227,0.0014,0.0010</t>
-  </si>
-  <si>
-    <t>0.9952,0.0015,0.0001,0.0007</t>
-  </si>
-  <si>
-    <t>0.9662,0.0417,0.0036,0.0014</t>
-  </si>
-  <si>
-    <t>0.9670,0.0344,0.0041,0.0013</t>
-  </si>
-  <si>
-    <t>0.9929,0.0019,0.0000,0.0016</t>
-  </si>
-  <si>
-    <t>0.0282,0.2384,0.8338,0.0042</t>
-  </si>
-  <si>
-    <t>0.0014,0.0485,0.9859,0.0024</t>
-  </si>
-  <si>
-    <t>0.0080,0.1092,0.9652,0.0069</t>
-  </si>
-  <si>
-    <t>0.1597,0.0108,0.8769,0.0037</t>
-  </si>
-  <si>
-    <t>0.0520,0.0160,0.9475,0.0030</t>
-  </si>
-  <si>
-    <t>0.1359,0.0527,0.7931,0.0396</t>
-  </si>
-  <si>
-    <t>0.2504,0.0026,0.8579,0.0026</t>
-  </si>
-  <si>
-    <t>0.0155,0.3376,0.5872,0.1881</t>
-  </si>
-  <si>
-    <t>0.8794,0.0018,0.0514,0.0313</t>
-  </si>
-  <si>
-    <t>0.0536,0.0867,0.0050,0.9639</t>
-  </si>
-  <si>
-    <t>0.0560,0.0022,0.0025,0.9751</t>
-  </si>
-  <si>
-    <t>0.0019,0.0006,0.0024,0.9979</t>
-  </si>
-  <si>
-    <t>0.0102,0.0016,0.0012,0.9951</t>
-  </si>
-  <si>
-    <t>0.4145,0.1634,0.0151,0.4566</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>0,1,0,1</t>
+  </si>
+  <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>0.8507,0.0283,0.0538,0.0359</t>
+  </si>
+  <si>
+    <t>0.0082,0.0057,0.0032,0.9941</t>
+  </si>
+  <si>
+    <t>0.2132,0.0024,0.0030,0.8940</t>
+  </si>
+  <si>
+    <t>0.1529,0.0057,0.0019,0.9364</t>
+  </si>
+  <si>
+    <t>0.9914,0.0072,0.0012,0.0004</t>
+  </si>
+  <si>
+    <t>0.9789,0.0226,0.0014,0.0013</t>
+  </si>
+  <si>
+    <t>0.9724,0.0233,0.0026,0.0030</t>
+  </si>
+  <si>
+    <t>0.9958,0.0006,0.0001,0.0012</t>
+  </si>
+  <si>
+    <t>0.9862,0.0121,0.0009,0.0012</t>
+  </si>
+  <si>
+    <t>0.9747,0.0202,0.0041,0.0016</t>
+  </si>
+  <si>
+    <t>0.9938,0.0004,0.0000,0.0040</t>
+  </si>
+  <si>
+    <t>0.9894,0.0030,0.0003,0.0025</t>
+  </si>
+  <si>
+    <t>0.6145,0.1322,0.1887,0.1440</t>
+  </si>
+  <si>
+    <t>0.0978,0.0766,0.8791,0.0024</t>
+  </si>
+  <si>
+    <t>0.4329,0.0160,0.6929,0.0033</t>
+  </si>
+  <si>
+    <t>0.1775,0.0390,0.8204,0.0029</t>
+  </si>
+  <si>
+    <t>0.8634,0.0103,0.0467,0.0399</t>
+  </si>
+  <si>
+    <t>0.0145,0.9783,0.0207,0.0003</t>
+  </si>
+  <si>
+    <t>0.0406,0.9563,0.0150,0.0010</t>
+  </si>
+  <si>
+    <t>0.2656,0.8117,0.0144,0.0036</t>
+  </si>
+  <si>
+    <t>0.0772,0.9209,0.0183,0.0031</t>
+  </si>
+  <si>
+    <t>0.0540,0.9447,0.0173,0.0026</t>
+  </si>
+  <si>
+    <t>0.5693,0.0318,0.3871,0.0793</t>
+  </si>
+  <si>
+    <t>0.4126,0.1072,0.1966,0.3636</t>
+  </si>
+  <si>
+    <t>0.0440,0.0041,0.9666,0.0013</t>
+  </si>
+  <si>
+    <t>0.2074,0.0688,0.7336,0.0172</t>
+  </si>
+  <si>
+    <t>0.0426,0.0106,0.9292,0.0241</t>
+  </si>
+  <si>
+    <t>0.1449,0.0067,0.9185,0.0009</t>
+  </si>
+  <si>
+    <t>0.0025,0.0083,0.9803,0.0154</t>
+  </si>
+  <si>
+    <t>0.4000,0.6336,0.0221,0.0018</t>
+  </si>
+  <si>
+    <t>0.7872,0.0535,0.1765,0.0103</t>
+  </si>
+  <si>
+    <t>0.0002,0.0064,0.9983,0.0004</t>
+  </si>
+  <si>
+    <t>0.0045,0.9103,0.3967,0.0003</t>
+  </si>
+  <si>
+    <t>0.8072,0.1905,0.0242,0.0089</t>
+  </si>
+  <si>
+    <t>0.8345,0.1375,0.0450,0.0087</t>
+  </si>
+  <si>
+    <t>0.6510,0.4340,0.0292,0.0014</t>
+  </si>
+  <si>
+    <t>0.1017,0.8231,0.3105,0.0093</t>
+  </si>
+  <si>
+    <t>0.0087,0.7884,0.3788,0.0539</t>
+  </si>
+  <si>
+    <t>0.1335,0.0642,0.8181,0.0370</t>
+  </si>
+  <si>
+    <t>0.0528,0.1061,0.7495,0.1766</t>
+  </si>
+  <si>
+    <t>0.2576,0.0030,0.6095,0.0480</t>
+  </si>
+  <si>
+    <t>0.0225,0.0422,0.9526,0.0043</t>
+  </si>
+  <si>
+    <t>0.0076,0.9271,0.0543,0.0080</t>
+  </si>
+  <si>
+    <t>0.1073,0.0697,0.8570,0.0073</t>
+  </si>
+  <si>
+    <t>0.1113,0.5964,0.0999,0.5710</t>
+  </si>
+  <si>
+    <t>0.0044,0.9791,0.0050,0.0059</t>
+  </si>
+  <si>
+    <t>0.0040,0.8309,0.8565,0.0009</t>
+  </si>
+  <si>
+    <t>0.0033,0.9810,0.0653,0.0030</t>
+  </si>
+  <si>
+    <t>0.0081,0.2390,0.8657,0.0433</t>
+  </si>
+  <si>
+    <t>0.0056,0.1099,0.9768,0.0019</t>
+  </si>
+  <si>
+    <t>0.0486,0.0024,0.9341,0.0213</t>
+  </si>
+  <si>
+    <t>0.1175,0.0068,0.9137,0.0070</t>
+  </si>
+  <si>
+    <t>0.0012,0.0049,0.9936,0.0022</t>
+  </si>
+  <si>
+    <t>0.0086,0.0646,0.9695,0.0025</t>
+  </si>
+  <si>
+    <t>0.9795,0.0164,0.0018,0.0014</t>
+  </si>
+  <si>
+    <t>0.9818,0.0039,0.0018,0.0046</t>
+  </si>
+  <si>
+    <t>0.8961,0.0794,0.0498,0.0025</t>
+  </si>
+  <si>
+    <t>0.0011,0.0965,0.9945,0.0002</t>
+  </si>
+  <si>
+    <t>0.9885,0.0037,0.0011,0.0017</t>
+  </si>
+  <si>
+    <t>0.9846,0.0068,0.0022,0.0023</t>
+  </si>
+  <si>
+    <t>0.9804,0.0144,0.0043,0.0009</t>
+  </si>
+  <si>
+    <t>0.0020,0.9247,0.7301,0.0015</t>
+  </si>
+  <si>
+    <t>0.0098,0.0793,0.9576,0.0111</t>
+  </si>
+  <si>
+    <t>0.0042,0.0284,0.9698,0.0288</t>
+  </si>
+  <si>
+    <t>0.0010,0.8830,0.9499,0.0003</t>
+  </si>
+  <si>
+    <t>0.0012,0.0026,0.9674,0.1085</t>
+  </si>
+  <si>
+    <t>0.0243,0.9553,0.0215,0.0004</t>
+  </si>
+  <si>
+    <t>0.0045,0.9772,0.0775,0.0001</t>
+  </si>
+  <si>
+    <t>0.6340,0.0465,0.4134,0.0137</t>
+  </si>
+  <si>
+    <t>0.6287,0.1289,0.3049,0.0158</t>
+  </si>
+  <si>
+    <t>0.0055,0.0394,0.9782,0.0037</t>
+  </si>
+  <si>
+    <t>0.0003,0.8931,0.9679,0.0001</t>
+  </si>
+  <si>
+    <t>0.0029,0.6933,0.9540,0.0005</t>
+  </si>
+  <si>
+    <t>0.0004,0.9832,0.5281,0.0004</t>
+  </si>
+  <si>
+    <t>0.0013,0.8491,0.9461,0.0005</t>
+  </si>
+  <si>
+    <t>0.1539,0.0036,0.0085,0.9129</t>
+  </si>
+  <si>
+    <t>0.0024,0.0034,0.0002,0.9985</t>
+  </si>
+  <si>
+    <t>0.0034,0.0871,0.0012,0.9923</t>
+  </si>
+  <si>
+    <t>0.0120,0.0109,0.0041,0.9909</t>
+  </si>
+  <si>
+    <t>0.0023,0.0061,0.0016,0.9973</t>
+  </si>
+  <si>
+    <t>0.0090,0.0072,0.0006,0.9953</t>
+  </si>
+  <si>
+    <t>0.0009,0.9584,0.8692,0.0002</t>
+  </si>
+  <si>
+    <t>0.0018,0.4577,0.9847,0.0001</t>
+  </si>
+  <si>
+    <t>0.0023,0.7988,0.9041,0.0005</t>
+  </si>
+  <si>
+    <t>0.0139,0.3085,0.9403,0.0022</t>
+  </si>
+  <si>
+    <t>0.0003,0.9671,0.9195,0.0001</t>
+  </si>
+  <si>
+    <t>0.0009,0.9331,0.8425,0.0001</t>
+  </si>
+  <si>
+    <t>0.9920,0.0073,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.9849,0.0236,0.0010,0.0003</t>
+  </si>
+  <si>
+    <t>0.9820,0.0153,0.0037,0.0006</t>
+  </si>
+  <si>
+    <t>0.9924,0.0021,0.0002,0.0017</t>
+  </si>
+  <si>
+    <t>0.9877,0.0065,0.0003,0.0018</t>
+  </si>
+  <si>
+    <t>0.9946,0.0009,0.0001,0.0019</t>
+  </si>
+  <si>
+    <t>0.9756,0.0298,0.0006,0.0014</t>
+  </si>
+  <si>
+    <t>0.9782,0.0198,0.0025,0.0011</t>
+  </si>
+  <si>
+    <t>0.9971,0.0003,0.0000,0.0011</t>
+  </si>
+  <si>
+    <t>0.9891,0.0074,0.0027,0.0004</t>
+  </si>
+  <si>
+    <t>0.9960,0.0012,0.0001,0.0007</t>
+  </si>
+  <si>
+    <t>0.9931,0.0015,0.0006,0.0013</t>
+  </si>
+  <si>
+    <t>0.9917,0.0025,0.0001,0.0020</t>
+  </si>
+  <si>
+    <t>0.9707,0.0275,0.0018,0.0026</t>
+  </si>
+  <si>
+    <t>0.9965,0.0005,0.0000,0.0011</t>
+  </si>
+  <si>
+    <t>0.9948,0.0011,0.0005,0.0008</t>
+  </si>
+  <si>
+    <t>0.0272,0.0028,0.9701,0.0128</t>
+  </si>
+  <si>
+    <t>0.1942,0.0060,0.6780,0.1056</t>
+  </si>
+  <si>
+    <t>0.8264,0.0021,0.0633,0.0375</t>
+  </si>
+  <si>
+    <t>0.0534,0.0410,0.8941,0.0188</t>
+  </si>
+  <si>
+    <t>0.1024,0.9263,0.0033,0.0008</t>
+  </si>
+  <si>
+    <t>0.0091,0.9847,0.0077,0.0003</t>
+  </si>
+  <si>
+    <t>0.1044,0.9144,0.0121,0.0011</t>
+  </si>
+  <si>
+    <t>0.2202,0.8031,0.0454,0.0054</t>
+  </si>
+  <si>
+    <t>0.0839,0.8668,0.0985,0.0006</t>
+  </si>
+  <si>
+    <t>0.0330,0.9686,0.0015,0.0005</t>
+  </si>
+  <si>
+    <t>0.3432,0.6651,0.0481,0.0026</t>
+  </si>
+  <si>
+    <t>0.4824,0.3728,0.1858,0.0348</t>
+  </si>
+  <si>
+    <t>0.1358,0.0738,0.8298,0.0072</t>
+  </si>
+  <si>
+    <t>0.4564,0.0475,0.5390,0.0165</t>
+  </si>
+  <si>
+    <t>0.5282,0.0633,0.4937,0.0067</t>
+  </si>
+  <si>
+    <t>0.1324,0.0859,0.0946,0.8510</t>
+  </si>
+  <si>
+    <t>0.0038,0.9838,0.0158,0.0028</t>
+  </si>
+  <si>
+    <t>0.0218,0.9265,0.0712,0.0355</t>
+  </si>
+  <si>
+    <t>0.0321,0.8850,0.0170,0.1621</t>
+  </si>
+  <si>
+    <t>0.0027,0.8178,0.9315,0.0005</t>
+  </si>
+  <si>
+    <t>0.0059,0.9820,0.0873,0.0001</t>
+  </si>
+  <si>
+    <t>0.5305,0.1841,0.3223,0.0017</t>
+  </si>
+  <si>
+    <t>0.5811,0.4968,0.0254,0.0015</t>
+  </si>
+  <si>
+    <t>0.9349,0.0506,0.0110,0.0044</t>
+  </si>
+  <si>
+    <t>0.9777,0.0035,0.0072,0.0026</t>
+  </si>
+  <si>
+    <t>0.9900,0.0009,0.0001,0.0057</t>
+  </si>
+  <si>
+    <t>0.9741,0.0055,0.0019,0.0097</t>
+  </si>
+  <si>
+    <t>0.9932,0.0011,0.0003,0.0016</t>
+  </si>
+  <si>
+    <t>0.9276,0.0281,0.0228,0.0102</t>
+  </si>
+  <si>
+    <t>0.9937,0.0009,0.0002,0.0019</t>
+  </si>
+  <si>
+    <t>0.9875,0.0017,0.0013,0.0039</t>
+  </si>
+  <si>
+    <t>0.0031,0.6994,0.9378,0.0007</t>
+  </si>
+  <si>
+    <t>0.0025,0.5709,0.9547,0.0001</t>
+  </si>
+  <si>
+    <t>0.0045,0.0955,0.9776,0.0017</t>
+  </si>
+  <si>
+    <t>0.0203,0.0522,0.9669,0.0014</t>
+  </si>
+  <si>
+    <t>0.8503,0.0230,0.0879,0.0110</t>
+  </si>
+  <si>
+    <t>0.7641,0.0608,0.1831,0.0054</t>
+  </si>
+  <si>
+    <t>0.8075,0.0176,0.2078,0.0054</t>
+  </si>
+  <si>
+    <t>0.6598,0.0867,0.2583,0.0398</t>
+  </si>
+  <si>
+    <t>0.1175,0.0010,0.0026,0.9461</t>
+  </si>
+  <si>
+    <t>0.0000,0.0047,0.0008,0.9995</t>
+  </si>
+  <si>
+    <t>0.0011,0.0376,0.0030,0.9956</t>
+  </si>
+  <si>
+    <t>0.0248,0.0028,0.0041,0.9874</t>
+  </si>
+  <si>
+    <t>0.0024,0.9028,0.7666,0.0011</t>
+  </si>
+  <si>
+    <t>0.9657,0.0183,0.0101,0.0035</t>
+  </si>
+  <si>
+    <t>0.6948,0.3763,0.0227,0.0080</t>
+  </si>
+  <si>
+    <t>0.9448,0.0502,0.0056,0.0045</t>
+  </si>
+  <si>
+    <t>0.3966,0.6868,0.0189,0.0010</t>
+  </si>
+  <si>
+    <t>0.9692,0.0084,0.0061,0.0057</t>
+  </si>
+  <si>
+    <t>0.0468,0.0211,0.0171,0.9646</t>
+  </si>
+  <si>
+    <t>0.9698,0.0067,0.0066,0.0055</t>
+  </si>
+  <si>
+    <t>0.0066,0.0299,0.9712,0.0219</t>
+  </si>
+  <si>
+    <t>0.9660,0.0004,0.0013,0.0276</t>
+  </si>
+  <si>
+    <t>0.9576,0.0009,0.0009,0.0454</t>
+  </si>
+  <si>
+    <t>0.1336,0.3005,0.7261,0.0037</t>
+  </si>
+  <si>
+    <t>0.8260,0.1638,0.0214,0.0057</t>
+  </si>
+  <si>
+    <t>0.8847,0.0404,0.0634,0.0043</t>
+  </si>
+  <si>
+    <t>0.6375,0.3792,0.0429,0.0044</t>
+  </si>
+  <si>
+    <t>0.6895,0.2164,0.1135,0.0184</t>
+  </si>
+  <si>
+    <t>0.8309,0.1429,0.0309,0.0060</t>
+  </si>
+  <si>
+    <t>0.9743,0.0072,0.0051,0.0047</t>
+  </si>
+  <si>
+    <t>0.9824,0.0037,0.0007,0.0059</t>
+  </si>
+  <si>
+    <t>0.9884,0.0027,0.0014,0.0025</t>
+  </si>
+  <si>
+    <t>0.9922,0.0019,0.0007,0.0013</t>
+  </si>
+  <si>
+    <t>0.9890,0.0051,0.0008,0.0013</t>
+  </si>
+  <si>
+    <t>0.9832,0.0047,0.0021,0.0036</t>
+  </si>
+  <si>
+    <t>0.9575,0.0280,0.0148,0.0029</t>
+  </si>
+  <si>
+    <t>0.9895,0.0020,0.0010,0.0026</t>
+  </si>
+  <si>
+    <t>0.5020,0.4705,0.0070,0.0305</t>
+  </si>
+  <si>
+    <t>0.7248,0.2877,0.0342,0.0008</t>
+  </si>
+  <si>
+    <t>0.5016,0.6108,0.0190,0.0031</t>
+  </si>
+  <si>
+    <t>0.7054,0.1802,0.1955,0.0315</t>
+  </si>
+  <si>
+    <t>0.9133,0.1302,0.0011,0.0024</t>
+  </si>
+  <si>
+    <t>0.9103,0.0781,0.0152,0.0060</t>
+  </si>
+  <si>
+    <t>0.8505,0.2295,0.0091,0.0018</t>
+  </si>
+  <si>
+    <t>0.5229,0.5580,0.0218,0.0029</t>
+  </si>
+  <si>
+    <t>0.0562,0.0381,0.9435,0.0055</t>
+  </si>
+  <si>
+    <t>0.8191,0.1547,0.0671,0.0070</t>
+  </si>
+  <si>
+    <t>0.0100,0.0307,0.9722,0.0033</t>
+  </si>
+  <si>
+    <t>0.0111,0.1044,0.9470,0.0108</t>
+  </si>
+  <si>
+    <t>0.3611,0.0088,0.7475,0.0081</t>
+  </si>
+  <si>
+    <t>0.0731,0.1649,0.8599,0.0079</t>
+  </si>
+  <si>
+    <t>0.0080,0.0030,0.9893,0.0026</t>
+  </si>
+  <si>
+    <t>0.0197,0.0041,0.9798,0.0027</t>
+  </si>
+  <si>
+    <t>0.0022,0.0640,0.9871,0.0014</t>
+  </si>
+  <si>
+    <t>0.4650,0.0908,0.5207,0.0113</t>
+  </si>
+  <si>
+    <t>0.1630,0.0242,0.8854,0.0018</t>
+  </si>
+  <si>
+    <t>0.5965,0.0942,0.3799,0.0399</t>
+  </si>
+  <si>
+    <t>0.2382,0.0229,0.8452,0.0012</t>
+  </si>
+  <si>
+    <t>0.2595,0.0758,0.6964,0.0206</t>
+  </si>
+  <si>
+    <t>0.3853,0.1158,0.4736,0.0026</t>
+  </si>
+  <si>
+    <t>0.4937,0.1486,0.3903,0.0227</t>
+  </si>
+  <si>
+    <t>0.4135,0.0988,0.5623,0.0081</t>
+  </si>
+  <si>
+    <t>0.5830,0.5465,0.0133,0.0010</t>
+  </si>
+  <si>
+    <t>0.3596,0.7329,0.0094,0.0013</t>
+  </si>
+  <si>
+    <t>0.6798,0.4814,0.0046,0.0024</t>
+  </si>
+  <si>
+    <t>0.8589,0.2190,0.0060,0.0036</t>
+  </si>
+  <si>
+    <t>0.9617,0.0531,0.0041,0.0010</t>
+  </si>
+  <si>
+    <t>0.4314,0.1659,0.4701,0.0372</t>
+  </si>
+  <si>
+    <t>0.8128,0.0138,0.1986,0.0035</t>
+  </si>
+  <si>
+    <t>0.7039,0.0625,0.0487,0.1348</t>
+  </si>
+  <si>
+    <t>0.6286,0.0293,0.2653,0.0780</t>
+  </si>
+  <si>
+    <t>0.7366,0.0206,0.2791,0.0104</t>
+  </si>
+  <si>
+    <t>0.3482,0.0325,0.6796,0.0123</t>
+  </si>
+  <si>
+    <t>0.0097,0.4561,0.9429,0.0039</t>
+  </si>
+  <si>
+    <t>0.0149,0.2465,0.9505,0.0069</t>
+  </si>
+  <si>
+    <t>0.0446,0.3066,0.8024,0.0311</t>
+  </si>
+  <si>
+    <t>0.0260,0.2932,0.8855,0.0148</t>
+  </si>
+  <si>
+    <t>0.9858,0.0079,0.0005,0.0024</t>
+  </si>
+  <si>
+    <t>0.9751,0.0284,0.0020,0.0010</t>
+  </si>
+  <si>
+    <t>0.9879,0.0046,0.0007,0.0023</t>
+  </si>
+  <si>
+    <t>0.9534,0.0638,0.0033,0.0021</t>
+  </si>
+  <si>
+    <t>0.9762,0.0202,0.0041,0.0013</t>
+  </si>
+  <si>
+    <t>0.9901,0.0081,0.0006,0.0008</t>
+  </si>
+  <si>
+    <t>0.9934,0.0006,0.0001,0.0028</t>
+  </si>
+  <si>
+    <t>0.9942,0.0012,0.0001,0.0016</t>
+  </si>
+  <si>
+    <t>0.1689,0.0360,0.8729,0.0032</t>
+  </si>
+  <si>
+    <t>0.3277,0.1886,0.5429,0.0264</t>
+  </si>
+  <si>
+    <t>0.1688,0.0138,0.6819,0.1592</t>
+  </si>
+  <si>
+    <t>0.0126,0.0192,0.9780,0.0032</t>
+  </si>
+  <si>
+    <t>0.0109,0.0254,0.9616,0.0086</t>
+  </si>
+  <si>
+    <t>0.0297,0.1418,0.8903,0.0021</t>
+  </si>
+  <si>
+    <t>0.0073,0.0082,0.9874,0.0023</t>
+  </si>
+  <si>
+    <t>0.0169,0.0630,0.9492,0.0019</t>
+  </si>
+  <si>
+    <t>0.0082,0.0153,0.9876,0.0010</t>
+  </si>
+  <si>
+    <t>0.0054,0.0550,0.9444,0.0309</t>
+  </si>
+  <si>
+    <t>0.0510,0.1924,0.8341,0.0016</t>
+  </si>
+  <si>
+    <t>0.7592,0.0236,0.1296,0.0392</t>
+  </si>
+  <si>
+    <t>0.6374,0.0173,0.4475,0.0051</t>
+  </si>
+  <si>
+    <t>0.9006,0.0045,0.0526,0.0130</t>
+  </si>
+  <si>
+    <t>0.9869,0.0130,0.0009,0.0008</t>
+  </si>
+  <si>
+    <t>0.9819,0.0120,0.0036,0.0012</t>
+  </si>
+  <si>
+    <t>0.9843,0.0103,0.0051,0.0005</t>
+  </si>
+  <si>
+    <t>0.9828,0.0113,0.0005,0.0020</t>
+  </si>
+  <si>
+    <t>0.9841,0.0046,0.0039,0.0021</t>
+  </si>
+  <si>
+    <t>0.9358,0.1243,0.0025,0.0004</t>
+  </si>
+  <si>
+    <t>0.9846,0.0121,0.0016,0.0012</t>
+  </si>
+  <si>
+    <t>0.9865,0.0056,0.0005,0.0026</t>
+  </si>
+  <si>
+    <t>0.0415,0.0269,0.9357,0.0027</t>
+  </si>
+  <si>
+    <t>0.0045,0.0160,0.9862,0.0045</t>
+  </si>
+  <si>
+    <t>0.0093,0.0297,0.9722,0.0032</t>
+  </si>
+  <si>
+    <t>0.0304,0.0244,0.9590,0.0029</t>
+  </si>
+  <si>
+    <t>0.0116,0.0068,0.9819,0.0062</t>
+  </si>
+  <si>
+    <t>0.0832,0.0106,0.9081,0.0290</t>
+  </si>
+  <si>
+    <t>0.0354,0.0129,0.9142,0.0740</t>
+  </si>
+  <si>
+    <t>0.0521,0.0629,0.7676,0.2110</t>
+  </si>
+  <si>
+    <t>0.8548,0.0063,0.0254,0.0938</t>
+  </si>
+  <si>
+    <t>0.0139,0.2952,0.0037,0.9600</t>
+  </si>
+  <si>
+    <t>0.0258,0.0492,0.0012,0.9773</t>
+  </si>
+  <si>
+    <t>0.0008,0.0047,0.0025,0.9982</t>
+  </si>
+  <si>
+    <t>0.0070,0.0113,0.0033,0.9942</t>
+  </si>
+  <si>
+    <t>0.5599,0.0498,0.0601,0.4026</t>
   </si>
 </sst>
 </file>
@@ -1956,7 +1965,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1970,7 +1979,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1981,10 +1990,10 @@
         <v>259</v>
       </c>
       <c r="C4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1998,7 +2007,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2012,7 +2021,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2026,7 +2035,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2040,7 +2049,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2054,7 +2063,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2068,7 +2077,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2082,7 +2091,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2096,7 +2105,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2110,7 +2119,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2121,10 +2130,10 @@
         <v>259</v>
       </c>
       <c r="C14" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2138,7 +2147,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2152,7 +2161,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2166,7 +2175,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2180,7 +2189,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2194,7 +2203,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2208,7 +2217,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2222,7 +2231,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2236,7 +2245,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2250,7 +2259,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2264,7 +2273,7 @@
         <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2275,10 +2284,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D25" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2292,7 +2301,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2306,7 +2315,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2320,7 +2329,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2334,7 +2343,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2348,7 +2357,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2362,7 +2371,7 @@
         <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2376,7 +2385,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2390,7 +2399,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2404,7 +2413,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2418,7 +2427,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2432,7 +2441,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2446,7 +2455,7 @@
         <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2460,7 +2469,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2471,10 +2480,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2488,7 +2497,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2502,7 +2511,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2516,7 +2525,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2530,7 +2539,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2544,7 +2553,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2558,7 +2567,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2569,10 +2578,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D46" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2586,7 +2595,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2597,10 +2606,10 @@
         <v>262</v>
       </c>
       <c r="C48" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D48" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2614,7 +2623,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2628,7 +2637,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2642,7 +2651,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2656,7 +2665,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2670,7 +2679,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2684,7 +2693,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2698,7 +2707,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2712,7 +2721,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2726,7 +2735,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2740,7 +2749,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2754,7 +2763,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2768,7 +2777,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2782,7 +2791,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2796,7 +2805,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2810,7 +2819,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2824,7 +2833,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2838,7 +2847,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2852,7 +2861,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2866,7 +2875,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2877,10 +2886,10 @@
         <v>262</v>
       </c>
       <c r="C68" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2894,7 +2903,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2908,7 +2917,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2922,7 +2931,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2936,7 +2945,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2950,7 +2959,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2964,7 +2973,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2978,7 +2987,7 @@
         <v>263</v>
       </c>
       <c r="D75" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2992,7 +3001,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3006,7 +3015,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3020,7 +3029,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3034,7 +3043,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3048,7 +3057,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3062,7 +3071,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3076,7 +3085,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3090,7 +3099,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3101,10 +3110,10 @@
         <v>261</v>
       </c>
       <c r="C84" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D84" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3115,10 +3124,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3129,10 +3138,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D86" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3146,7 +3155,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3160,7 +3169,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3174,7 +3183,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3188,7 +3197,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3202,7 +3211,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3216,7 +3225,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3230,7 +3239,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3244,7 +3253,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3258,7 +3267,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3272,7 +3281,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3286,7 +3295,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3300,7 +3309,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3314,7 +3323,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3328,7 +3337,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3342,7 +3351,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3356,7 +3365,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3370,7 +3379,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3384,7 +3393,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3398,7 +3407,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3412,7 +3421,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3426,7 +3435,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3440,7 +3449,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3454,7 +3463,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3468,7 +3477,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3482,7 +3491,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3496,7 +3505,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3510,7 +3519,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3524,7 +3533,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3538,7 +3547,7 @@
         <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3549,10 +3558,10 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D116" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3566,7 +3575,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3577,10 +3586,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D118" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3594,7 +3603,7 @@
         <v>259</v>
       </c>
       <c r="D119" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3608,7 +3617,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3622,7 +3631,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3636,7 +3645,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3650,7 +3659,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3664,7 +3673,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3678,7 +3687,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3692,7 +3701,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3703,10 +3712,10 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3720,7 +3729,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3734,7 +3743,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3748,7 +3757,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3762,7 +3771,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3776,7 +3785,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3790,7 +3799,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3804,7 +3813,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3818,7 +3827,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3832,7 +3841,7 @@
         <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3846,7 +3855,7 @@
         <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3860,7 +3869,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3874,7 +3883,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3885,10 +3894,10 @@
         <v>259</v>
       </c>
       <c r="C140" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3902,7 +3911,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3913,10 +3922,10 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D142" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3930,7 +3939,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3944,7 +3953,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3958,7 +3967,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3972,7 +3981,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3986,7 +3995,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3997,10 +4006,10 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4014,7 +4023,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4028,7 +4037,7 @@
         <v>259</v>
       </c>
       <c r="D150" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4042,7 +4051,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4053,10 +4062,10 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4070,7 +4079,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4081,10 +4090,10 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4098,7 +4107,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4112,7 +4121,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4126,7 +4135,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4140,7 +4149,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4151,10 +4160,10 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D159" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4168,7 +4177,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4182,7 +4191,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4196,7 +4205,7 @@
         <v>259</v>
       </c>
       <c r="D162" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4210,7 +4219,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4224,7 +4233,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4238,7 +4247,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4252,7 +4261,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4266,7 +4275,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4280,7 +4289,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4294,7 +4303,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4308,7 +4317,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4322,7 +4331,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4336,7 +4345,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4347,10 +4356,10 @@
         <v>259</v>
       </c>
       <c r="C173" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4361,10 +4370,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4375,10 +4384,10 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="D175" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4392,7 +4401,7 @@
         <v>259</v>
       </c>
       <c r="D176" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4406,7 +4415,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4420,7 +4429,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4434,7 +4443,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4445,10 +4454,10 @@
         <v>259</v>
       </c>
       <c r="C180" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D180" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4462,7 +4471,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4476,7 +4485,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4490,7 +4499,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4504,7 +4513,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4518,7 +4527,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4532,7 +4541,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4546,7 +4555,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4560,7 +4569,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4574,7 +4583,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4588,7 +4597,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4602,7 +4611,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4616,7 +4625,7 @@
         <v>259</v>
       </c>
       <c r="D192" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4630,7 +4639,7 @@
         <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4644,7 +4653,7 @@
         <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4655,10 +4664,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D195" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4669,10 +4678,10 @@
         <v>259</v>
       </c>
       <c r="C196" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D196" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4683,10 +4692,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4697,10 +4706,10 @@
         <v>259</v>
       </c>
       <c r="C198" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D198" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4714,7 +4723,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4728,7 +4737,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4742,7 +4751,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4753,10 +4762,10 @@
         <v>259</v>
       </c>
       <c r="C202" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4767,10 +4776,10 @@
         <v>259</v>
       </c>
       <c r="C203" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D203" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4784,7 +4793,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4798,7 +4807,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4812,7 +4821,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4826,7 +4835,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4840,7 +4849,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4854,7 +4863,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4868,7 +4877,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4882,7 +4891,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4893,10 +4902,10 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4910,7 +4919,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4924,7 +4933,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4938,7 +4947,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4952,7 +4961,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4966,7 +4975,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4980,7 +4989,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4994,7 +5003,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5008,7 +5017,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5022,7 +5031,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5033,10 +5042,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5047,10 +5056,10 @@
         <v>259</v>
       </c>
       <c r="C223" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D223" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5064,7 +5073,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5078,7 +5087,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5089,10 +5098,10 @@
         <v>261</v>
       </c>
       <c r="C226" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5106,7 +5115,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5120,7 +5129,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5134,7 +5143,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5148,7 +5157,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5162,7 +5171,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5176,7 +5185,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5190,7 +5199,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5204,7 +5213,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5218,7 +5227,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5232,7 +5241,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5246,7 +5255,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5260,7 +5269,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5274,7 +5283,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5288,7 +5297,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5302,7 +5311,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5316,7 +5325,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5330,7 +5339,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5344,7 +5353,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5358,7 +5367,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5372,7 +5381,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5386,7 +5395,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5400,7 +5409,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5414,7 +5423,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5428,7 +5437,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5442,7 +5451,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5456,7 +5465,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5470,7 +5479,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5484,7 +5493,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5498,7 +5507,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5512,7 +5521,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
     </row>
   </sheetData>
